--- a/06_附件资料/监管组织&用户导入模板.xlsx
+++ b/06_附件资料/监管组织&用户导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13500" activeTab="2"/>
+    <workbookView windowWidth="30720" windowHeight="13500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="填写说明" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="103">
   <si>
     <t>监管组织&amp;用户导入模板 - 填写说明</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>自定义住宅装修类型</t>
+  </si>
+  <si>
+    <t>自定义零星作业类型</t>
   </si>
   <si>
     <t>自定义小型工程作业场所</t>
@@ -547,7 +550,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -568,6 +571,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor theme="4" tint="0.799981688894314"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -753,12 +762,123 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="27">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -994,7 +1114,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
@@ -1006,119 +1126,119 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="13">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="14">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="13">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="15">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="23">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="24">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="25">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="26">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1138,6 +1258,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1161,28 +1282,40 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -1557,258 +1690,258 @@
   <dimension ref="A1:G27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="35.8888888888889" style="32" customWidth="1"/>
-    <col min="2" max="3" width="15" style="32" customWidth="1"/>
-    <col min="4" max="4" width="29.1111111111111" style="32" customWidth="1"/>
-    <col min="5" max="5" width="25" style="32" customWidth="1"/>
-    <col min="6" max="6" width="55" style="32" customWidth="1"/>
-    <col min="7" max="7" width="40" style="32" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="32"/>
+    <col min="1" max="1" width="35.8888888888889" style="37" customWidth="1"/>
+    <col min="2" max="3" width="15" style="37" customWidth="1"/>
+    <col min="4" max="4" width="29.1111111111111" style="37" customWidth="1"/>
+    <col min="5" max="5" width="25" style="37" customWidth="1"/>
+    <col min="6" max="6" width="55" style="37" customWidth="1"/>
+    <col min="7" max="7" width="40" style="37" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="37"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.4" spans="1:7">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="39" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:7">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="41" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="39" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="37" t="s">
+      <c r="G15" s="42" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="42" t="s">
+      <c r="D16" s="47" t="s">
         <v>21</v>
       </c>
       <c r="E16" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="42" t="s">
+      <c r="F16" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="G16" s="42" t="s">
+      <c r="G16" s="47" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="42" t="s">
+      <c r="D17" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="42" t="s">
+      <c r="F17" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="42" t="s">
+      <c r="G17" s="47" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="42" t="s">
+      <c r="D18" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="42" t="s">
+      <c r="F18" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="42" t="s">
+      <c r="G18" s="47" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="42" t="s">
+      <c r="D19" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="F19" s="42" t="s">
+      <c r="F19" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="G19" s="42" t="s">
+      <c r="G19" s="47" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="D20" s="42" t="s">
+      <c r="D20" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="42" t="s">
+      <c r="F20" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="42" t="s">
+      <c r="G20" s="47" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="D21" s="42" t="s">
+      <c r="D21" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="F21" s="42" t="s">
+      <c r="F21" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="G21" s="42" t="s">
+      <c r="G21" s="47" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="D22" s="42" t="s">
+      <c r="D22" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="F22" s="42" t="s">
+      <c r="F22" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="G22" s="42" t="s">
+      <c r="G22" s="47" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="D23" s="42" t="s">
+      <c r="D23" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="42" t="s">
+      <c r="F23" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="G23" s="42" t="s">
+      <c r="G23" s="47" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="D24" s="42" t="s">
+      <c r="D24" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="42" t="s">
+      <c r="F24" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="G24" s="42" t="s">
+      <c r="G24" s="47" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" spans="2:7">
-      <c r="D25" s="42" t="s">
+      <c r="D25" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="F25" s="42" t="s">
+      <c r="F25" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="G25" s="42" t="s">
+      <c r="G25" s="47" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="26" spans="2:7">
-      <c r="D26" s="42" t="s">
+      <c r="D26" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="G26" s="42" t="s">
+      <c r="G26" s="47" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="D27" s="42" t="s">
+      <c r="D27" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="G27" s="42" t="s">
+      <c r="G27" s="47" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1844,116 +1977,116 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="23" customHeight="1" spans="1:7">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="27" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="21" customHeight="1" spans="1:7">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7" t="s">
+      <c r="D2" s="29"/>
+      <c r="E2" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="26"/>
+      <c r="G2" s="30"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:7">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12" t="s">
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="28"/>
+      <c r="G3" s="33"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:7">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7" t="s">
+      <c r="D4" s="29"/>
+      <c r="E4" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="G4" s="26"/>
+      <c r="G4" s="30"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:7">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12" t="s">
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="G5" s="28"/>
+      <c r="G5" s="33"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="20.25" customHeight="1" spans="1:7">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30" t="s">
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="31"/>
+      <c r="G6" s="36"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="34.5" customHeight="1"/>
     <row r="8" s="1" customFormat="1" ht="20.25" customHeight="1"/>
@@ -2016,7 +2149,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13.712962962963" customWidth="1"/>
@@ -2025,12 +2158,13 @@
     <col min="4" max="4" width="11.8611111111111" customWidth="1"/>
     <col min="5" max="5" width="9.72222222222222" customWidth="1"/>
     <col min="6" max="6" width="51.9814814814815" style="1" customWidth="1"/>
-    <col min="7" max="7" width="31.4907407407407" customWidth="1"/>
-    <col min="8" max="8" width="28.6666666666667" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="7" max="7" width="33.6203703703704" customWidth="1"/>
+    <col min="8" max="8" width="31.4907407407407" customWidth="1"/>
+    <col min="9" max="9" width="28.6666666666667" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" spans="1:9">
+    <row r="1" ht="18.75" customHeight="1" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>78</v>
       </c>
@@ -2055,19 +2189,22 @@
       <c r="H1" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="3" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="2" ht="24" customHeight="1" spans="1:9">
+      <c r="J1" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:10">
       <c r="A2" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>19</v>
@@ -2076,102 +2213,106 @@
         <v>26</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="9"/>
+      <c r="I2" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="9"/>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="1:9">
-      <c r="A3" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" s="11" t="s">
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:10">
+      <c r="A3" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="C3" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="13"/>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:9">
-      <c r="A4" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="15" t="s">
+      <c r="F3" s="13"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="14"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:10">
+      <c r="A4" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="C4" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="16" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="9"/>
-    </row>
-    <row r="5" ht="28.8" spans="1:9">
-      <c r="A5" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" s="17" t="s">
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="10"/>
+    </row>
+    <row r="5" ht="28.8" spans="1:10">
+      <c r="A5" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="C5" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
+      <c r="F5" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
       <c r="I5" s="20"/>
+      <c r="J5" s="21"/>
     </row>
     <row r="6" ht="24" customHeight="1"/>
-    <row r="7" ht="69" customHeight="1" spans="1:9">
-      <c r="A7" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
+    <row r="7" ht="69" customHeight="1" spans="1:10">
+      <c r="A7" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
     </row>
     <row r="8" ht="24" customHeight="1"/>
     <row r="9" ht="24" customHeight="1"/>
     <row r="10" ht="24" customHeight="1"/>
     <row r="11" ht="24" customHeight="1"/>
-    <row r="12" ht="24" customHeight="1" spans="1:9">
-      <c r="A12" s="22"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="23"/>
+    <row r="12" ht="24" customHeight="1" spans="1:10">
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="24"/>
     </row>
     <row r="13" ht="24" customHeight="1"/>
     <row r="14" ht="24" customHeight="1"/>
@@ -2297,7 +2438,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="输入错误" error="请从下拉列表中选择权限模式" promptTitle="权限模式" prompt="请选择权限模式" sqref="E3:E10000">
       <formula1>填写说明!$C$16:$C$17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="输入错误" error="请从下拉列表中选择" promptTitle="住宅装修类型" prompt="请选择住宅装修类型" sqref="G3:G10000">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="输入错误" error="请从下拉列表中选择" promptTitle="住宅装修类型" prompt="请选择住宅装修类型" sqref="G3:G10000 H3:H10000">
       <formula1>填写说明!$E$16:$E$16</formula1>
     </dataValidation>
   </dataValidations>
